--- a/artifacts/任务规格转化.xlsx
+++ b/artifacts/任务规格转化.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="Rb23127a87eab4907"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="R4e4da468c0394ea1"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/artifacts/任务规格转化.xlsx
+++ b/artifacts/任务规格转化.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="R4e4da468c0394ea1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="R1277b0418087488d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -367,15 +367,15 @@
         <x:v>输入来源</x:v>
       </x:c>
       <x:c r="B5" s="9" t="str">
-        <x:v>脱敏订阅偏好发布材料，包括本地页面、用户资料、同意策略和保存旅程</x:v>
+        <x:v>本次订阅偏好发布使用的本地页面、用户资料、同意策略和保存旅程，身份字段已经脱敏</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="47" customHeight="1">
       <x:c r="A6" s="9" t="str">
-        <x:v>输入获取方式</x:v>
+        <x:v>业务目标</x:v>
       </x:c>
       <x:c r="B6" s="9" t="str">
-        <x:v>解压输入数据包后，在input_data目录读取app、fixtures、starter、scripts和tools</x:v>
+        <x:v>检查订阅偏好发布中的同意限制、版本请求、失败回滚和键盘路径，为发布负责人提供状态与回滚记录</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="92" customHeight="1">
@@ -396,10 +396,10 @@
     </x:row>
     <x:row r="9" ht="47" customHeight="1">
       <x:c r="A9" s="9" t="str">
-        <x:v>核心操作链</x:v>
+        <x:v>软件步骤</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
-        <x:v>读取资料与规则；配置Chromium；建立隔离浏览器会话；接管三个接口；操作订阅表单；捕获请求；观察回滚；走键盘路径；整理三份报告</x:v>
+        <x:v>用Playwright配置Chromium并建立独立浏览器会话，接管三个本地接口后操作订阅表单、捕获请求、观察回滚、走键盘路径并整理三份报告</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="47" customHeight="1">
@@ -436,10 +436,10 @@
     </x:row>
     <x:row r="14" ht="47" customHeight="1">
       <x:c r="A14" s="9" t="str">
-        <x:v>会话与网络边界</x:v>
+        <x:v>实现边界</x:v>
       </x:c>
       <x:c r="B14" s="9" t="str">
-        <x:v>焦点检查及每条保存旅程使用独立browser context，正式运行只访问本机回环地址</x:v>
+        <x:v>焦点检查及每条保存旅程使用独立browser context，浏览器只访问本机回环地址</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="47" customHeight="1">
@@ -452,26 +452,26 @@
     </x:row>
     <x:row r="16" ht="47" customHeight="1">
       <x:c r="A16" s="9" t="str">
-        <x:v>完成条件</x:v>
+        <x:v>交付要求</x:v>
       </x:c>
       <x:c r="B16" s="9" t="str">
-        <x:v>npm run process返回0，五个目标路径可读，三份报告与浏览器观察及公开输入一致</x:v>
+        <x:v>交付Playwright配置、完成版浏览器测试和三份CSV，报告与浏览器观察及随包规则一致</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="47" customHeight="1">
       <x:c r="A17" s="9" t="str">
-        <x:v>可验证点</x:v>
+        <x:v>业务核对</x:v>
       </x:c>
       <x:c r="B17" s="9" t="str">
-        <x:v>Chromium项目、context隔离、route端点、PUT版本头与正文、最终开关、aria-live文案、activeElement次序</x:v>
+        <x:v>核对Chromium项目、context隔离、route端点、PUT版本头与正文、最终开关、aria-live文案和activeElement次序</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="47" customHeight="1">
       <x:c r="A18" s="9" t="str">
-        <x:v>不适合作为评分点的内容</x:v>
+        <x:v>允许变体</x:v>
       </x:c>
       <x:c r="B18" s="9" t="str">
-        <x:v>辅助函数拆分、变量名、注释、内部对象、等价定位器、CSV必要引号以及LF或CRLF行尾</x:v>
+        <x:v>辅助函数、变量名、注释、内部对象和等价定位器可以不同；CSV可使用必要引号以及LF或CRLF行尾</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
